--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260708.xlsx
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,411,296</t>
+          <t>181,515</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>181,515</t>
+          <t>5,411,296</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>805,897</t>
+          <t>575,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>575,000</t>
+          <t>805,897</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>4,440,578</t>
+          <t>1,374,384</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>3,469,981</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,374,384</t>
+          <t>3,469,981</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>4,440,578</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>774,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>774,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>289,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,752,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>1,752,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>253,000</t>
+          <t>330,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>330,000</t>
+          <t>253,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>335,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>335,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
